--- a/ics_topologies/electrical_substation/electrical_substation.xlsx
+++ b/ics_topologies/electrical_substation/electrical_substation.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R20"/>
+  <dimension ref="A1:S20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,65 +445,70 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>purdue_level</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>description</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>criticality</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>vendor</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>model</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>ip</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>cvss_type</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>exposed</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>patched</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>consequence_severity</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>role</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>awareness</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>privilege</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>p_base_override</t>
         </is>
@@ -537,49 +542,54 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
           <t>Firewall to utility WAN</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Cisco</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>ASA 5585</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
         <is>
           <t>7.5</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -609,49 +619,54 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
           <t>Core substation Ethernet switch</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Siemens</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>RUGGEDCOM RSG920P</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -681,49 +696,54 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
           <t>Gateway to utility SCADA</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>GE</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>D400</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
         <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>9.0</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -753,49 +773,54 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
           <t>Operator interface</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>Siemens</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>SIMATIC HMI</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
         <is>
           <t>7.5</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -825,49 +850,54 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
           <t>Configuration laptop</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>Dell</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Latitude 5420</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
         <is>
           <t>7.8</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -897,49 +927,54 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>Remote Terminal Unit for data acquisition</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>Schweitzer</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>SEL-3530</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
         <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>8.0</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -969,49 +1004,54 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>Distance protection relay</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>Siemens</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="J8" t="inlineStr">
         <is>
           <t>SIPROTEC 5 7SA86</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
         <is>
           <t>7.5</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>9.0</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1041,49 +1081,54 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t>Transformer differential protection</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>Siemens</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>SIPROTEC 5 7UT86</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
         <is>
           <t>7.5</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>9.0</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1113,49 +1158,54 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
           <t>Busbar protection</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>Siemens</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>SIPROTEC 5 7SS86</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
         <is>
           <t>7.5</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>9.0</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1185,49 +1235,54 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
           <t>PMU for synchrophasors</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>GE</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>PMU 369</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1257,49 +1312,54 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
           <t>IEC 61850 process interface</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>Siemens</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>SIO 6MD85</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1329,37 +1389,42 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
           <t>High voltage circuit breaker</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>ABB</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>HPL 550</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr">
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
         <is>
           <t>10.0</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr">
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
@@ -1393,37 +1458,42 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
           <t>Disconnecting switch</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>Siemens</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>8DA10</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr">
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
         <is>
           <t>7.0</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr">
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
@@ -1457,37 +1527,42 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
           <t>Main step-down transformer</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>High</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>Siemens</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>TRAFO 100 MVA</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr">
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
         <is>
           <t>10.0</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr">
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr">
         <is>
           <t>0.02</t>
         </is>
@@ -1521,37 +1596,42 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
           <t>Capacitive voltage transformer</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>ABB</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>CPD 1</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr">
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
         <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr">
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
@@ -1585,37 +1665,42 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
           <t>Current transformer</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>ABB</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>CT 1000:1</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr">
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
         <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr">
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
@@ -1649,37 +1734,42 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
           <t>Oil temperature sensor</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>Emerson</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>Rosemount 214</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr">
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
         <is>
           <t>5.0</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr">
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
@@ -1713,37 +1803,42 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
           <t>SF6 gas density monitor</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>WIKA</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>GDM-100</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr">
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
         <is>
           <t>6.0</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr">
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
@@ -1777,41 +1872,46 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
           <t>Utility dispatcher supervising the substation</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr">
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr">
         <is>
           <t>3.0</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>operator</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>0.45</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>standard</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1824,7 +1924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1858,6 +1958,16 @@
           <t>trust</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>firewalled</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>transport</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1890,6 +2000,12 @@
           <t>low</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1922,6 +2038,8 @@
           <t>high</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1954,6 +2072,8 @@
           <t>high</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1986,6 +2106,8 @@
           <t>high</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2018,6 +2140,8 @@
           <t>high</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2050,6 +2174,8 @@
           <t>high</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2082,6 +2208,8 @@
           <t>high</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2114,6 +2242,8 @@
           <t>high</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2146,6 +2276,8 @@
           <t>high</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2178,6 +2310,8 @@
           <t>low</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2210,6 +2344,8 @@
           <t>low</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2242,6 +2378,8 @@
           <t>low</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2274,6 +2412,8 @@
           <t>low</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2306,6 +2446,8 @@
           <t>low</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2338,6 +2480,8 @@
           <t>low</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2370,6 +2514,8 @@
           <t>low</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2402,6 +2548,8 @@
           <t>low</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2434,6 +2582,8 @@
           <t>low</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2466,6 +2616,8 @@
           <t>high</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2498,6 +2650,8 @@
           <t>medium</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
